--- a/docs/parameter-hallucination/shortcut-gap-reanalysis/chat/chat_cli_param_hallucination_analysis.xlsx
+++ b/docs/parameter-hallucination/shortcut-gap-reanalysis/chat/chat_cli_param_hallucination_analysis.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇报总览" sheetId="1" r:id="R7d092a322e814584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数问题明细" sheetId="2" r:id="R8e49888efaf34db6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兜底解决方案" sheetId="3" r:id="Rc99aceee5fa6495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前无法解决" sheetId="4" r:id="R05ceae5ff4d648ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析依据" sheetId="5" r:id="R0f571b437fe84bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇报总览" sheetId="1" r:id="R1ead1065ab544cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数问题明细" sheetId="2" r:id="R872336ecd6cd4818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兜底解决方案" sheetId="3" r:id="R14e8c6d5a8bd4f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前无法解决" sheetId="4" r:id="Re3cfd02d89a84b14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析依据" sheetId="5" r:id="R0ea2eea910034083"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -532,7 +532,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>冻结基线 5f906bf8b61bc54a75f6c2b46219a1deb682b600｜正式别名表未修改｜候选、报告、五页工作簿独立交付</x:v>
+        <x:v>冻结基线 f4474b57eb1db23b1638b9574be2f5dca368a360｜正式别名表未修改｜候选、报告、五页工作簿独立交付</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -592,7 +592,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="56" t="str">
-        <x:v>结论：候选变更 9 个 concept、18 个 command override、66 条 fixture；逐产品生成与政策门禁均通过。</x:v>
+        <x:v>结论：候选变更 9 个 concept、18 个 command override、67 条 fixture；逐产品生成与政策门禁均通过。</x:v>
       </x:c>
       <x:c r="B8" s="57"/>
       <x:c r="C8" s="57"/>
@@ -762,7 +762,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>冻结基线 5f906bf8b61bc54a75f6c2b46219a1deb682b600｜逐命令核对真实 Help/Cobra、运行时 Schema、Skill 与正式别名表</x:v>
+        <x:v>冻结基线 f4474b57eb1db23b1638b9574be2f5dca368a360｜逐命令核对真实 Help/Cobra、运行时 Schema、Skill 与正式别名表</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -877,7 +877,7 @@
         <x:v>limit 是总量上限且没有 cursor；role 是枚举</x:v>
       </x:c>
       <x:c r="E8" s="19" t="str">
-        <x:v>size 别名可归一；cursor 阻断；type 歧义</x:v>
+        <x:v>仅 max-results / max-result 归一到总量上限；分页式命名阻断，generic size/type 保持歧义</x:v>
       </x:c>
       <x:c r="F8" s="19" t="str">
         <x:v>部分兜底</x:v>
@@ -1243,7 +1243,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>仅接受同实体、同角色、同值域、同基数且值原样传递的映射；共新增 66 条 fixture</x:v>
+        <x:v>仅接受同实体、同角色、同值域、同基数且值原样传递的映射；共新增 67 条 fixture</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -1311,7 +1311,6 @@
       <x:c r="D6" s="19" t="str">
         <x:v>chat +conversation-list
 chat +conversation-list-top
-chat +chat-list-mine
 chat +chat-list-all
 chat +chat-list-join-requests
 chat +at-me
@@ -1576,7 +1575,7 @@
         <x:v>chat +chat-list-mine</x:v>
       </x:c>
       <x:c r="C17" s="18" t="str">
-        <x:v>bind 1 / block 4 / ambiguous 1</x:v>
+        <x:v>alias 2 / block 6 / ambiguous 4</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
         <x:v>chat +chat-list-mine</x:v>
@@ -1585,7 +1584,7 @@
         <x:v>仅在本命令启用已验证的 bind / scoped alias；其余近似参数保持拦截或歧义保护</x:v>
       </x:c>
       <x:c r="F17" s="18" t="str">
-        <x:v>cursor, page-token, page, offset, type</x:v>
+        <x:v>cursor, page-token, page, offset, page-size, per-page, type, size, take, top</x:v>
       </x:c>
       <x:c r="G17" s="18" t="str">
         <x:v>严格命令域</x:v>
@@ -2048,7 +2047,7 @@
         <x:v>部分兜底</x:v>
       </x:c>
       <x:c r="E8" s="19" t="str">
-        <x:v>size 别名可归一；cursor 阻断；type 歧义</x:v>
+        <x:v>仅 max-results / max-result 保留原值映射；page-size / per-page 阻断，size / take / top 与 type 保持歧义</x:v>
       </x:c>
       <x:c r="F8" s="19" t="str">
         <x:v>需修改真实 CLI/框架，或由 Agent 明确选择真实参数；别名表不做查找、转换、枚举翻译或基数变化</x:v>
@@ -2348,7 +2347,7 @@
         <x:v>冻结基线</x:v>
       </x:c>
       <x:c r="B5" s="18" t="str">
-        <x:v>origin/main@5f906bf8b61bc54a75f6c2b46219a1deb682b600</x:v>
+        <x:v>origin/main@f4474b57eb1db23b1638b9574be2f5dca368a360</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
         <x:v>通过</x:v>
